--- a/posicoes/Nome fundos e prev.xlsx
+++ b/posicoes/Nome fundos e prev.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CCA291-10AA-4CF0-99C5-B8506AA2704D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DA4F89-4AAA-4D3E-ADBB-546C8752481D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4AAAD741-8AD6-4B77-B1DE-59D8D73093AB}"/>
+    <workbookView xWindow="28845" yWindow="-16380" windowWidth="29040" windowHeight="15840" xr2:uid="{4AAAD741-8AD6-4B77-B1DE-59D8D73093AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Fundos de Investimentos" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8957" uniqueCount="2440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8624" uniqueCount="2439">
   <si>
     <t>NOME_FUNDO</t>
   </si>
@@ -5930,10 +5930,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Carência inicial para Port. Internas
-(dias corridos)</t>
   </si>
   <si>
     <t>Gestor Estratégico</t>
@@ -7188,9 +7184,6 @@
     <t>Ações Internacional</t>
   </si>
   <si>
-    <t>D+999</t>
-  </si>
-  <si>
     <t>Safra Vitesse Classe de Investimento RF CP RL</t>
   </si>
   <si>
@@ -7351,6 +7344,9 @@
   </si>
   <si>
     <t xml:space="preserve"> XP VISTA ASSET MANAGMENT LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidação </t>
   </si>
 </sst>
 </file>
@@ -7496,7 +7492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -7522,13 +7518,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 4" xfId="1" xr:uid="{33BA684D-A6D2-4816-B56D-744E24CE78A6}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7536,14 +7538,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8291,13 +8285,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="B13" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="C13" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -8332,7 +8326,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="D14" t="s">
         <v>340</v>
@@ -8346,7 +8340,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="J15">
         <v>30</v>
@@ -8404,7 +8398,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="D17" t="s">
         <v>98</v>
@@ -8418,7 +8412,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="D18" t="s">
         <v>98</v>
@@ -9509,7 +9503,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="D49" t="s">
         <v>283</v>
@@ -9695,7 +9689,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="D55" t="s">
         <v>340</v>
@@ -12934,7 +12928,7 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="B143" t="s">
         <v>14</v>
@@ -13089,7 +13083,7 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="B147" t="s">
         <v>821</v>
@@ -13419,7 +13413,7 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="B156" t="s">
         <v>136</v>
@@ -13460,7 +13454,7 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="B157" t="s">
         <v>128</v>
@@ -13539,10 +13533,10 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="B159" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="C159" t="s">
         <v>129</v>
@@ -13618,7 +13612,7 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="B161" t="s">
         <v>741</v>
@@ -13738,7 +13732,7 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="B164" t="s">
         <v>1214</v>
@@ -13747,7 +13741,7 @@
         <v>1215</v>
       </c>
       <c r="D164" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="E164" t="s">
         <v>786</v>
@@ -14224,7 +14218,7 @@
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="D182" t="s">
         <v>16</v>
@@ -14655,7 +14649,7 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="D195" t="s">
         <v>16</v>
@@ -15045,7 +15039,7 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="B207" t="s">
         <v>1806</v>
@@ -15471,7 +15465,7 @@
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="D219" t="s">
         <v>16</v>
@@ -16155,7 +16149,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="B240" t="s">
         <v>1845</v>
@@ -16164,7 +16158,7 @@
         <v>464</v>
       </c>
       <c r="D240" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="E240" t="s">
         <v>37</v>
@@ -16449,7 +16443,7 @@
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="B250" t="s">
         <v>1430</v>
@@ -16490,10 +16484,10 @@
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="B251" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="C251" t="s">
         <v>632</v>
@@ -17446,7 +17440,7 @@
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="B276" t="s">
         <v>1253</v>
@@ -19585,7 +19579,7 @@
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" s="11" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="D339" t="s">
         <v>283</v>
@@ -19675,13 +19669,13 @@
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="B342" t="s">
         <v>1619</v>
       </c>
       <c r="C342" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="D342" t="s">
         <v>98</v>
@@ -19754,13 +19748,13 @@
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="B344" t="s">
         <v>1823</v>
       </c>
       <c r="C344" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="D344" t="s">
         <v>98</v>
@@ -19836,7 +19830,7 @@
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="D346" t="s">
         <v>16</v>
@@ -19891,13 +19885,13 @@
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="B348" t="s">
         <v>1682</v>
       </c>
       <c r="C348" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="D348" t="s">
         <v>16</v>
@@ -20174,7 +20168,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="D356" t="s">
         <v>98</v>
@@ -20278,7 +20272,7 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="J360">
         <v>0</v>
@@ -20295,16 +20289,16 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="B361" t="s">
         <v>1774</v>
       </c>
       <c r="C361" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="D361" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="E361" t="s">
         <v>485</v>
@@ -20391,7 +20385,7 @@
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="D364" t="s">
         <v>16</v>
@@ -20676,7 +20670,7 @@
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="D373" t="s">
         <v>16</v>
@@ -21804,7 +21798,7 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="D406" t="s">
         <v>16</v>
@@ -21818,7 +21812,7 @@
     </row>
     <row r="407" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="B407" t="s">
         <v>433</v>
@@ -22063,10 +22057,10 @@
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="B414" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="C414" t="s">
         <v>247</v>
@@ -22156,7 +22150,7 @@
     </row>
     <row r="417" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="D417" t="s">
         <v>340</v>
@@ -22170,7 +22164,7 @@
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="D418" t="s">
         <v>16</v>
@@ -22511,7 +22505,7 @@
     </row>
     <row r="428" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="D428" t="s">
         <v>16</v>
@@ -24984,7 +24978,7 @@
     </row>
     <row r="496" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="B496" t="s">
         <v>642</v>
@@ -25698,7 +25692,7 @@
         <v>83</v>
       </c>
       <c r="D514" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="E514" t="s">
         <v>309</v>
@@ -25739,7 +25733,7 @@
         <v>83</v>
       </c>
       <c r="D515" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="E515" t="s">
         <v>450</v>
@@ -26893,7 +26887,7 @@
     </row>
     <row r="546" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="D546" t="s">
         <v>16</v>
@@ -27749,7 +27743,7 @@
     </row>
     <row r="569" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D569" t="s">
         <v>440</v>
@@ -29309,7 +29303,7 @@
     </row>
     <row r="611" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="B611" t="s">
         <v>1054</v>
@@ -29426,7 +29420,7 @@
     </row>
     <row r="614" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="C614" t="s">
         <v>29</v>
@@ -29563,7 +29557,7 @@
     </row>
     <row r="618" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="B618" t="s">
         <v>1666</v>
@@ -29759,7 +29753,7 @@
     </row>
     <row r="623" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="D623" t="s">
         <v>16</v>
@@ -29814,7 +29808,7 @@
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="D625" t="s">
         <v>16</v>
@@ -29828,7 +29822,7 @@
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="D626" t="s">
         <v>16</v>
@@ -30543,7 +30537,7 @@
     </row>
     <row r="646" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="D646" t="s">
         <v>16</v>
@@ -30595,7 +30589,7 @@
     </row>
     <row r="648" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="B648" t="s">
         <v>1126</v>
@@ -31575,7 +31569,7 @@
     </row>
     <row r="673" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="D673" t="s">
         <v>16</v>
@@ -31589,7 +31583,7 @@
     </row>
     <row r="674" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="B674" t="s">
         <v>1608</v>
@@ -31598,7 +31592,7 @@
         <v>1609</v>
       </c>
       <c r="D674" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="E674" t="s">
         <v>485</v>
@@ -32987,7 +32981,7 @@
     </row>
     <row r="710" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="D710" t="s">
         <v>16</v>
@@ -34339,7 +34333,7 @@
     </row>
     <row r="747" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="D747" t="s">
         <v>16</v>
@@ -34353,7 +34347,7 @@
     </row>
     <row r="748" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="D748" t="s">
         <v>16</v>
@@ -34367,10 +34361,10 @@
     </row>
     <row r="749" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="B749" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="C749" t="s">
         <v>231</v>
@@ -35722,7 +35716,7 @@
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="J786">
         <v>0</v>
@@ -35739,7 +35733,7 @@
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="J787">
         <v>0</v>
@@ -37664,7 +37658,7 @@
     </row>
     <row r="839" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A839" s="10" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="B839" t="s">
         <v>1645</v>
@@ -37673,7 +37667,7 @@
         <v>165</v>
       </c>
       <c r="D839" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="E839" t="s">
         <v>485</v>
@@ -37801,7 +37795,7 @@
     </row>
     <row r="843" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="D843" t="s">
         <v>36</v>
@@ -40201,13 +40195,13 @@
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="B909" t="s">
         <v>982</v>
       </c>
       <c r="C909" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="D909" t="s">
         <v>16</v>
@@ -40321,7 +40315,7 @@
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="D912" t="s">
         <v>16</v>
@@ -40335,16 +40329,16 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="B913" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="C913" t="s">
         <v>29</v>
       </c>
       <c r="D913" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="E913" t="s">
         <v>485</v>
@@ -40418,7 +40412,7 @@
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="D917" t="s">
         <v>16</v>
@@ -41001,7 +40995,7 @@
     </row>
     <row r="934" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="D934" t="s">
         <v>16</v>
@@ -41324,7 +41318,7 @@
       </c>
     </row>
     <row r="943" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A943" s="13" t="s">
+      <c r="A943" t="s">
         <v>251</v>
       </c>
       <c r="B943" t="s">
@@ -41362,7 +41356,7 @@
       </c>
     </row>
     <row r="944" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A944" s="13" t="s">
+      <c r="A944" t="s">
         <v>303</v>
       </c>
       <c r="B944" t="s">
@@ -41400,7 +41394,7 @@
       </c>
     </row>
     <row r="945" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A945" s="13" t="s">
+      <c r="A945" t="s">
         <v>1675</v>
       </c>
       <c r="B945" t="s">
@@ -42681,11 +42675,12 @@
     <col min="1" max="1" width="38.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.44140625" style="14" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>1964</v>
       </c>
@@ -42695,28 +42690,28 @@
       <c r="C1" s="5" t="s">
         <v>1966</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="13" t="s">
+        <v>2438</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>1967</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>1968</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B2" s="8">
         <v>47612701000145</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D2" s="15">
+        <v>999</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>409</v>
@@ -42727,16 +42722,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B3" s="8">
         <v>29242441000181</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D3" s="15">
+        <v>999</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>409</v>
@@ -42747,19 +42742,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B4" s="8">
         <v>48212959000117</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D4" s="15">
+        <v>999</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>287</v>
@@ -42767,16 +42762,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B5" s="8">
         <v>25681955000182</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D5" s="15">
+        <v>999</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>774</v>
@@ -42787,99 +42782,99 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B6" s="8">
         <v>34081155000111</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D6" s="15">
+        <v>999</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>1977</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B7" s="8">
         <v>29722458000136</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D7" s="15">
+        <v>999</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B8" s="8">
         <v>29732909000116</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D8" s="15">
+        <v>999</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>1057</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B9" s="8">
         <v>20814969000103</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D9" s="15">
+        <v>999</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>1057</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B10" s="8">
         <v>50128847000124</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D10" s="15">
+        <v>999</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>786</v>
@@ -42887,16 +42882,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B11" s="8">
         <v>31353579000108</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D11" s="15">
+        <v>999</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>203</v>
@@ -42907,56 +42902,56 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B12" s="8">
         <v>3879361000148</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D12" s="15">
+        <v>999</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>203</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B13" s="8">
         <v>46375144000123</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D13" s="15">
+        <v>999</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>203</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B14" s="8">
         <v>44211899000167</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D14" s="15">
+        <v>999</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>394</v>
@@ -42967,56 +42962,56 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B15" s="8">
         <v>29045319000115</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D15" s="15">
+        <v>999</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>1373</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B16" s="8">
         <v>33520932000114</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D16" s="15">
+        <v>999</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B17" s="8">
         <v>28911614000144</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D17" s="15">
+        <v>999</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>269</v>
@@ -43027,36 +43022,36 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B18" s="8">
         <v>34442059000151</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D18" s="15">
+        <v>999</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>269</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B19" s="8">
         <v>29562424000121</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D19" s="15">
+        <v>999</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>269</v>
@@ -43067,19 +43062,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B20" s="8">
         <v>23263359000157</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D20" s="15">
+        <v>999</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>786</v>
@@ -43087,16 +43082,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B21" s="8">
         <v>24405282000175</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D21" s="15">
+        <v>999</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>1060</v>
@@ -43107,19 +43102,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B22" s="8">
         <v>27239065000140</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D22" s="15">
+        <v>999</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>786</v>
@@ -43127,19 +43122,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B23" s="8">
         <v>26498249000162</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D23" s="15">
+        <v>999</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>786</v>
@@ -43147,19 +43142,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B24" s="8">
         <v>29626006000150</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D24" s="15">
+        <v>999</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>253</v>
@@ -43167,59 +43162,59 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B25" s="8">
         <v>30178912000119</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D25" s="15">
+        <v>999</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B26" s="8">
         <v>38033115000155</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D26" s="15">
+        <v>999</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>960</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B27" s="8">
         <v>30068728000116</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D27" s="15">
+        <v>999</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>786</v>
@@ -43227,36 +43222,36 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B28" s="8">
         <v>38281397000100</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D28" s="15">
+        <v>999</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>943</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B29" s="8">
         <v>26343792000190</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D29" s="15">
+        <v>999</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>518</v>
@@ -43267,16 +43262,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B30" s="8">
         <v>42535455000151</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D30" s="15">
+        <v>999</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>1254</v>
@@ -43287,56 +43282,56 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B31" s="8">
         <v>45605046000172</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D31" s="15">
+        <v>999</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>1543</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B32" s="8">
         <v>29800227000101</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D32" s="15">
+        <v>999</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B33" s="8">
         <v>18041877000196</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D33" s="15">
+        <v>999</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>1165</v>
@@ -43347,16 +43342,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B34" s="8">
         <v>45511041000180</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D34" s="15">
+        <v>999</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>1165</v>
@@ -43367,39 +43362,39 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B35" s="8">
         <v>12823627000121</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D35" s="15">
+        <v>999</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B36" s="8">
         <v>21818801000139</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D36" s="15">
+        <v>999</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>253</v>
@@ -43407,16 +43402,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B37" s="8">
         <v>15862867000123</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D37" s="15">
+        <v>999</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>753</v>
@@ -43427,19 +43422,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B38" s="8">
         <v>21494444000109</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D38" s="15">
+        <v>999</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>786</v>
@@ -43447,19 +43442,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B39" s="8">
         <v>46685502000102</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D39" s="15">
+        <v>999</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>786</v>
@@ -43467,19 +43462,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B40" s="8">
         <v>45444101000190</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D40" s="15">
+        <v>999</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>485</v>
@@ -43487,19 +43482,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B41" s="8">
         <v>46762380000100</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D41" s="15">
+        <v>999</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>786</v>
@@ -43507,19 +43502,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B42" s="8">
         <v>36352241000147</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D42" s="15">
+        <v>999</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>485</v>
@@ -43527,59 +43522,59 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B43" s="8">
         <v>36617562000126</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D43" s="15">
+        <v>999</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B44" s="8">
         <v>4228716000100</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D44" s="15">
+        <v>999</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B45" s="8">
         <v>29045219000199</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D45" s="15">
+        <v>999</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>287</v>
@@ -43587,99 +43582,99 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B46" s="8">
         <v>46192463000101</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D46" s="15">
+        <v>999</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B47" s="8">
         <v>7190746000154</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D47" s="15">
+        <v>999</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B48" s="8">
         <v>7190735000174</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D48" s="15">
+        <v>999</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B49" s="8">
         <v>35636610000160</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D49" s="15">
+        <v>999</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B50" s="8">
         <v>3537456000183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D50" s="15">
+        <v>999</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>270</v>
@@ -43687,79 +43682,79 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B51" s="8">
         <v>33520901000163</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D51" s="15">
+        <v>999</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B52" s="8">
         <v>29732967000140</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D52" s="15">
+        <v>999</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>1317</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B53" s="8">
         <v>39723078000170</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D53" s="15">
+        <v>999</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B54" s="8">
         <v>29275210000174</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D54" s="15">
+        <v>999</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>274</v>
@@ -43767,39 +43762,39 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B55" s="8">
         <v>35807793000130</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D55" s="15">
+        <v>999</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B56" s="8">
         <v>38015773000114</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D56" s="15">
+        <v>999</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>274</v>
@@ -43807,16 +43802,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B57" s="8">
         <v>41505673000180</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D57" s="15">
+        <v>999</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>1137</v>
@@ -43827,39 +43822,39 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B58" s="8">
         <v>35314803000103</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D58" s="15">
+        <v>999</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B59" s="8">
         <v>11098129000109</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D59" s="15">
+        <v>999</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>98</v>
@@ -43867,56 +43862,56 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B60" s="8">
         <v>37844994000132</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D60" s="15">
+        <v>999</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B61" s="8">
         <v>27328750000143</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D61" s="15">
+        <v>999</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>101</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B62" s="8">
         <v>26180316000104</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D62" s="15">
+        <v>999</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>259</v>
@@ -43927,19 +43922,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="B63" s="8">
         <v>17685620000104</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D63" s="15">
+        <v>999</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>270</v>
@@ -43947,19 +43942,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B64" s="8">
         <v>30869348000180</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D64" s="15">
+        <v>999</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>274</v>
@@ -43967,19 +43962,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="B65" s="8">
         <v>37332385000102</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D65" s="15">
+        <v>999</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>287</v>
@@ -43987,79 +43982,79 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="B66" s="8">
         <v>40213012000119</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D66" s="15">
+        <v>999</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="B67" s="8">
         <v>44643002000174</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D67" s="15">
+        <v>999</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="B68" s="8">
         <v>31340875000166</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D68" s="15">
+        <v>999</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>1394</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="B69" s="8">
         <v>12796193000118</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D69" s="15">
+        <v>999</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>786</v>
@@ -44067,19 +44062,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="B70" s="8">
         <v>31248460000167</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D70" s="15">
+        <v>999</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>253</v>
@@ -44087,39 +44082,39 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="B71" s="8">
         <v>41127450000127</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D71" s="15">
+        <v>999</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="B72" s="8">
         <v>26710546000120</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D72" s="15">
+        <v>999</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>16</v>
@@ -44127,19 +44122,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="B73" s="8">
         <v>28692448000132</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D73" s="15">
+        <v>999</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>274</v>
@@ -44147,19 +44142,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="B74" s="8">
         <v>41424063000152</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D74" s="15">
+        <v>999</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>274</v>
@@ -44167,39 +44162,39 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="B75" s="8">
         <v>40386490000120</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D75" s="15">
+        <v>999</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="B76" s="8">
         <v>42014145000191</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D76" s="15">
+        <v>999</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>485</v>
@@ -44207,56 +44202,56 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="B77" s="8">
         <v>34793027000109</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D77" s="15">
+        <v>999</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>923</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="B78" s="8">
         <v>35610342000108</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D78" s="15">
+        <v>999</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>1309</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B79" s="8">
         <v>29733120000180</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D79" s="15">
+        <v>999</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>1144</v>
@@ -44267,16 +44262,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="B80" s="8">
         <v>41163524000180</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D80" s="15">
+        <v>999</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>154</v>
@@ -44287,19 +44282,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B81" s="8">
         <v>23339936000147</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D81" s="15">
+        <v>999</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>98</v>
@@ -44307,39 +44302,39 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B82" s="8">
         <v>35363972000125</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D82" s="15">
+        <v>999</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="B83" s="8">
         <v>23964741000198</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D83" s="15">
+        <v>999</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>274</v>
@@ -44347,19 +44342,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B84" s="8">
         <v>27974819000106</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D84" s="15">
+        <v>999</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>274</v>
@@ -44367,19 +44362,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B85" s="8">
         <v>9166056000195</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D85" s="15">
+        <v>999</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>786</v>
@@ -44387,39 +44382,39 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="B86" s="8">
         <v>23872787000187</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D86" s="15">
+        <v>999</v>
       </c>
       <c r="E86" s="7" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F86" s="7" t="s">
         <v>2099</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B87" s="8">
         <v>36820361000121</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D87" s="15">
+        <v>999</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>270</v>
@@ -44427,19 +44422,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B88" s="8">
         <v>18927174000160</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D88" s="15">
+        <v>999</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>253</v>
@@ -44447,59 +44442,59 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B89" s="8">
         <v>18897562000145</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D89" s="15">
+        <v>999</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="B90" s="8">
         <v>33701805000111</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D90" s="15">
+        <v>999</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>203</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B91" s="8">
         <v>22759978000174</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D91" s="15">
+        <v>999</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>274</v>
@@ -44507,39 +44502,39 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B92" s="8">
         <v>28516168000173</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D92" s="15">
+        <v>999</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>1011</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B93" s="8">
         <v>23502671000156</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D93" s="15">
+        <v>999</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>786</v>
@@ -44547,79 +44542,79 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B94" s="8">
         <v>20889471000100</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D94" s="15">
+        <v>999</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B95" s="8">
         <v>29091970000121</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D95" s="15">
+        <v>999</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>1165</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B96" s="8">
         <v>4616035000100</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D96" s="15">
+        <v>999</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="B97" s="8">
         <v>39598187000102</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D97" s="15">
+        <v>999</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>287</v>
@@ -44627,59 +44622,59 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="B98" s="8">
         <v>13768597000160</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D98" s="15">
+        <v>999</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="B99" s="8">
         <v>10394850000175</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D99" s="15">
+        <v>999</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B100" s="8">
         <v>19959552000150</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D100" s="15">
+        <v>999</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>786</v>
@@ -44687,16 +44682,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="B101" s="8">
         <v>19922130000100</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D101" s="15">
+        <v>999</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>42</v>
@@ -44707,19 +44702,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="B102" s="8">
         <v>44409267000102</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D102" s="15">
+        <v>999</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>287</v>
@@ -44727,56 +44722,56 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B103" s="8">
         <v>52955280000195</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D103" s="15">
+        <v>999</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B104" s="8">
         <v>37355605000105</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D104" s="15">
+        <v>999</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>409</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="B105" s="8">
         <v>40882496000199</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D105" s="15">
+        <v>999</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>409</v>
@@ -44787,19 +44782,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="B106" s="8">
         <v>37541379000157</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D106" s="15">
+        <v>999</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>287</v>
@@ -44807,16 +44802,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="B107" s="8">
         <v>41610515000190</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D107" s="15">
+        <v>999</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>774</v>
@@ -44827,16 +44822,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="B108" s="8">
         <v>30998045000168</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D108" s="15">
+        <v>999</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>774</v>
@@ -44847,19 +44842,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="B109" s="8">
         <v>47020683000102</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D109" s="15">
+        <v>999</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>786</v>
@@ -44867,139 +44862,139 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="B110" s="8">
         <v>35939857000156</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D110" s="15">
+        <v>999</v>
       </c>
       <c r="E110" s="7" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F110" s="7" t="s">
         <v>1977</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="B111" s="8">
         <v>32757743000105</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D111" s="15">
+        <v>999</v>
       </c>
       <c r="E111" s="7" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F111" s="7" t="s">
         <v>1977</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="B112" s="8">
         <v>35939700000120</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D112" s="15">
+        <v>999</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="B113" s="8">
         <v>32761323000194</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D113" s="15">
+        <v>999</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="B114" s="8">
         <v>40779573000180</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D114" s="15">
+        <v>999</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="B115" s="8">
         <v>37124157000139</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D115" s="15">
+        <v>999</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>1057</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="B116" s="8">
         <v>42794534000187</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D116" s="15">
+        <v>999</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>270</v>
@@ -45007,16 +45002,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="B117" s="8">
         <v>32318938000140</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D117" s="15">
+        <v>999</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>203</v>
@@ -45027,59 +45022,59 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B118" s="8">
         <v>34461754000160</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D118" s="15">
+        <v>999</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>203</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="B119" s="8">
         <v>40212715000122</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D119" s="15">
+        <v>999</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>203</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B120" s="8">
         <v>45645218000131</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D120" s="15">
+        <v>999</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>287</v>
@@ -45087,16 +45082,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B121" s="8">
         <v>51188983000172</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D121" s="15">
+        <v>999</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>394</v>
@@ -45107,36 +45102,36 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="B122" s="8">
         <v>35956270000155</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D122" s="15">
+        <v>999</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>1373</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="B123" s="8">
         <v>53482542000104</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D123" s="15">
+        <v>999</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>56</v>
@@ -45147,16 +45142,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="B124" s="8">
         <v>45298150000161</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D124" s="15">
+        <v>999</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>269</v>
@@ -45167,16 +45162,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B125" s="8">
         <v>32847001000162</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D125" s="15">
+        <v>999</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>269</v>
@@ -45187,36 +45182,36 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B126" s="8">
         <v>43779069000178</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D126" s="15">
+        <v>999</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>269</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B127" s="8">
         <v>40799759000109</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D127" s="15">
+        <v>999</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>269</v>
@@ -45227,19 +45222,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B128" s="8">
         <v>39281327000114</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D128" s="15">
+        <v>999</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>274</v>
@@ -45247,36 +45242,36 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B129" s="8">
         <v>45645241000126</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D129" s="15">
+        <v>999</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B130" s="8">
         <v>51673830000110</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D130" s="15">
+        <v>999</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>15</v>
@@ -45287,19 +45282,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B131" s="8">
         <v>41610532000128</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D131" s="15">
+        <v>999</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>270</v>
@@ -45307,36 +45302,36 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="B132" s="8">
         <v>51675442000179</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D132" s="15">
+        <v>999</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>742</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B133" s="8">
         <v>52986170000190</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D133" s="15">
+        <v>999</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>742</v>
@@ -45347,59 +45342,59 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B134" s="8">
         <v>34187279000186</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D134" s="15">
+        <v>999</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>926</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B135" s="8">
         <v>32892517000129</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D135" s="15">
+        <v>999</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>926</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="B136" s="8">
         <v>51675926000118</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D136" s="15">
+        <v>999</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>786</v>
@@ -45407,16 +45402,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="B137" s="8">
         <v>37396759000145</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D137" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D137" s="15">
+        <v>999</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>1060</v>
@@ -45427,19 +45422,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B138" s="8">
         <v>32319658000157</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D138" s="15">
+        <v>999</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F138" s="7" t="s">
         <v>786</v>
@@ -45447,39 +45442,39 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="B139" s="8">
         <v>43779018000146</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D139" s="15">
+        <v>999</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B140" s="8">
         <v>35955948000185</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D140" s="15">
+        <v>999</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F140" s="7" t="s">
         <v>485</v>
@@ -45487,19 +45482,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B141" s="8">
         <v>32755077000168</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D141" s="15">
+        <v>999</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F141" s="7" t="s">
         <v>253</v>
@@ -45507,19 +45502,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B142" s="8">
         <v>37396828000110</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D142" s="15">
+        <v>999</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F142" s="7" t="s">
         <v>287</v>
@@ -45527,39 +45522,39 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="7" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B143" s="8">
         <v>36318550000109</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D143" s="15">
+        <v>999</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="B144" s="8">
         <v>35651477000111</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D144" s="15">
+        <v>999</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>98</v>
@@ -45567,99 +45562,99 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B145" s="8">
         <v>36327214000114</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D145" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D145" s="15">
+        <v>999</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>960</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="B146" s="8">
         <v>43761805000160</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D146" s="15">
+        <v>999</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>960</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="B147" s="8">
         <v>31963337000128</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D147" s="15">
+        <v>999</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>960</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B148" s="8">
         <v>37645515000159</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D148" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D148" s="15">
+        <v>999</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>960</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="B149" s="8">
         <v>35420731000170</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D149" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D149" s="15">
+        <v>999</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F149" s="7" t="s">
         <v>270</v>
@@ -45667,159 +45662,159 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B150" s="8">
         <v>41866111000162</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D150" s="15">
+        <v>999</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B151" s="8">
         <v>41802178000133</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D151" s="15">
+        <v>999</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="7" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B152" s="8">
         <v>35364038000128</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D152" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D152" s="15">
+        <v>999</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>431</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B153" s="8">
         <v>40212923000121</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D153" s="15">
+        <v>999</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>943</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="7" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B154" s="8">
         <v>42870699000190</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D154" s="15">
+        <v>999</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>943</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="B155" s="8">
         <v>32319047000109</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D155" s="15">
+        <v>999</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="7" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="B156" s="8">
         <v>40781467000130</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D156" s="15">
+        <v>999</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="B157" s="8">
         <v>35956326000171</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D157" s="15">
+        <v>999</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>287</v>
@@ -45827,16 +45822,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="B158" s="8">
         <v>43215421000142</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D158" s="15">
+        <v>999</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>518</v>
@@ -45847,16 +45842,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="B159" s="8">
         <v>40635018000184</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D159" s="15">
+        <v>999</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>1038</v>
@@ -45867,16 +45862,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B160" s="8">
         <v>42535297000130</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D160" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D160" s="15">
+        <v>999</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>1254</v>
@@ -45887,36 +45882,36 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="B161" s="8">
         <v>43859993000164</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D161" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D161" s="15">
+        <v>999</v>
       </c>
       <c r="E161" s="7" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F161" s="7" t="s">
         <v>2187</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>2188</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="7" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="B162" s="8">
         <v>32847791000186</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D162" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D162" s="15">
+        <v>999</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>877</v>
@@ -45927,16 +45922,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="B163" s="8">
         <v>47020660000106</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D163" s="15">
+        <v>999</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>877</v>
@@ -45947,96 +45942,96 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="7" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="B164" s="8">
         <v>44409327000197</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D164" s="15">
+        <v>999</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>1543</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="B165" s="8">
         <v>35956641000107</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D165" s="15">
+        <v>999</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>1543</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="B166" s="8">
         <v>39992897000112</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D166" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D166" s="15">
+        <v>999</v>
       </c>
       <c r="E166" s="7" t="s">
+        <v>2193</v>
+      </c>
+      <c r="F166" s="7" t="s">
         <v>2194</v>
-      </c>
-      <c r="F166" s="7" t="s">
-        <v>2195</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="B167" s="8">
         <v>40779216000111</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D167" s="15">
+        <v>999</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="B168" s="8">
         <v>44409353000115</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D168" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D168" s="15">
+        <v>999</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>1165</v>
@@ -46047,16 +46042,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="B169" s="8">
         <v>36620088000191</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D169" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D169" s="15">
+        <v>999</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>1165</v>
@@ -46067,16 +46062,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B170" s="8">
         <v>44409430000137</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D170" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D170" s="15">
+        <v>999</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>1165</v>
@@ -46087,39 +46082,39 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="B171" s="8">
         <v>40655014000168</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D171" s="15">
+        <v>999</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>1317</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B172" s="8">
         <v>35955960000190</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D172" s="15">
+        <v>999</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="F172" s="7" t="s">
         <v>98</v>
@@ -46127,19 +46122,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B173" s="8">
         <v>32849785000168</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D173" s="15">
+        <v>999</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="F173" s="7" t="s">
         <v>786</v>
@@ -46147,39 +46142,39 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B174" s="8">
         <v>47020776000137</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D174" s="15">
+        <v>999</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B175" s="8">
         <v>45756511000176</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D175" s="15">
+        <v>999</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F175" s="7" t="s">
         <v>287</v>
@@ -46187,39 +46182,39 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="B176" s="8">
         <v>50236261000183</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D176" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D176" s="15">
+        <v>999</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B177" s="8">
         <v>49227982000148</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D177" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D177" s="15">
+        <v>999</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F177" s="7" t="s">
         <v>786</v>
@@ -46227,19 +46222,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="7" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="B178" s="8">
         <v>47020727000102</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D178" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D178" s="15">
+        <v>999</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F178" s="7" t="s">
         <v>485</v>
@@ -46247,19 +46242,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B179" s="8">
         <v>32319225000100</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D179" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D179" s="15">
+        <v>999</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F179" s="7" t="s">
         <v>16</v>
@@ -46267,39 +46262,39 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B180" s="8">
         <v>35704530000103</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D180" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D180" s="15">
+        <v>999</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="B181" s="8">
         <v>34474500000187</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D181" s="15">
+        <v>999</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F181" s="7" t="s">
         <v>274</v>
@@ -46307,16 +46302,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="7" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="B182" s="8">
         <v>44815039000132</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D182" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D182" s="15">
+        <v>999</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>97</v>
@@ -46327,56 +46322,56 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="B183" s="8">
         <v>44434888000146</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D183" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D183" s="15">
+        <v>999</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>753</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="B184" s="8">
         <v>40781292000161</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D184" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D184" s="15">
+        <v>999</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>753</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B185" s="8">
         <v>30898110000183</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D185" s="15">
+        <v>999</v>
       </c>
       <c r="E185" s="7" t="s">
         <v>753</v>
@@ -46387,36 +46382,36 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B186" s="8">
         <v>40635009000193</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D186" s="15">
+        <v>999</v>
       </c>
       <c r="E186" s="7" t="s">
         <v>753</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B187" s="8">
         <v>40679129000192</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D187" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D187" s="15">
+        <v>999</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>1137</v>
@@ -46427,16 +46422,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="7" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="B188" s="8">
         <v>42847502000100</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D188" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D188" s="15">
+        <v>999</v>
       </c>
       <c r="E188" s="7" t="s">
         <v>1137</v>
@@ -46447,16 +46442,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="B189" s="8">
         <v>43636203000181</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D189" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D189" s="15">
+        <v>999</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>247</v>
@@ -46467,16 +46462,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="7" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="B190" s="8">
         <v>35162484000150</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D190" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D190" s="15">
+        <v>999</v>
       </c>
       <c r="E190" s="7" t="s">
         <v>247</v>
@@ -46487,16 +46482,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B191" s="8">
         <v>37728799000147</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D191" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D191" s="15">
+        <v>999</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>247</v>
@@ -46507,76 +46502,76 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="7" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="B192" s="8">
         <v>52998678000109</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D192" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D192" s="15">
+        <v>999</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>247</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B193" s="8">
         <v>37053502000190</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D193" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D193" s="15">
+        <v>999</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>247</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="B194" s="8">
         <v>32973280000100</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D194" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D194" s="15">
+        <v>999</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>247</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="B195" s="8">
         <v>32864403000175</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D195" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D195" s="15">
+        <v>999</v>
       </c>
       <c r="E195" s="7" t="s">
         <v>247</v>
@@ -46587,76 +46582,76 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="7" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B196" s="8">
         <v>36352287000166</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D196" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D196" s="15">
+        <v>999</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>1324</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B197" s="8">
         <v>34462068000104</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D197" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D197" s="15">
+        <v>999</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="B198" s="8">
         <v>27793095000102</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D198" s="15">
+        <v>999</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B199" s="8">
         <v>45645166000101</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D199" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D199" s="15">
+        <v>999</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>184</v>
@@ -46667,16 +46662,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="B200" s="8">
         <v>34287126000100</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D200" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D200" s="15">
+        <v>999</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>184</v>
@@ -46687,16 +46682,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="B201" s="8">
         <v>42195844000185</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D201" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D201" s="15">
+        <v>999</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>184</v>
@@ -46707,59 +46702,59 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B202" s="8">
         <v>47033051000183</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D202" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D202" s="15">
+        <v>999</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B203" s="8">
         <v>43860692000150</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D203" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D203" s="15">
+        <v>999</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="7" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B204" s="8">
         <v>40682081000171</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D204" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D204" s="15">
+        <v>999</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>450</v>
@@ -46767,36 +46762,36 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B205" s="8">
         <v>45645112000138</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D205" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D205" s="15">
+        <v>999</v>
       </c>
       <c r="E205" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B206" s="8">
         <v>32385140000111</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D206" s="15">
+        <v>999</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>26</v>
@@ -46807,39 +46802,39 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B207" s="8">
         <v>36327253000111</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D207" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D207" s="15">
+        <v>999</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>978</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B208" s="8">
         <v>33345639000168</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D208" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D208" s="15">
+        <v>999</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="F208" s="7" t="s">
         <v>274</v>
@@ -46847,76 +46842,76 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="B209" s="8">
         <v>36318499000127</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D209" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D209" s="15">
+        <v>999</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="7" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B210" s="8">
         <v>34475121000101</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D210" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D210" s="15">
+        <v>999</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>1350</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="7" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B211" s="8">
         <v>37037432000187</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D211" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D211" s="15">
+        <v>999</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>957</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="7" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B212" s="8">
         <v>38249045000177</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D212" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D212" s="15">
+        <v>999</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>259</v>
@@ -46927,59 +46922,59 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="7" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B213" s="8">
         <v>38035023000104</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D213" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D213" s="15">
+        <v>999</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>259</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="7" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B214" s="8">
         <v>43423418000114</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D214" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D214" s="15">
+        <v>999</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="B215" s="8">
         <v>40780979000182</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D215" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D215" s="15">
+        <v>999</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F215" s="7" t="s">
         <v>253</v>
@@ -46987,19 +46982,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="7" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="B216" s="8">
         <v>32312361000160</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D216" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D216" s="15">
+        <v>999</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F216" s="7" t="s">
         <v>270</v>
@@ -47007,79 +47002,79 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="7" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="B217" s="8">
         <v>38236291000194</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D217" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D217" s="15">
+        <v>999</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>1314</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="7" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="B218" s="8">
         <v>39958567000100</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D218" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D218" s="15">
+        <v>999</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>1314</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="7" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="B219" s="8">
         <v>37396739000174</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D219" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D219" s="15">
+        <v>999</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="7" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="B220" s="8">
         <v>33755685000135</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D220" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D220" s="15">
+        <v>999</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>287</v>
@@ -47087,36 +47082,36 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="7" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="B221" s="8">
         <v>33796214000175</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D221" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D221" s="15">
+        <v>999</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="7" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="B222" s="8">
         <v>34400740000137</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D222" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D222" s="15">
+        <v>999</v>
       </c>
       <c r="E222" s="7" t="s">
         <v>162</v>
@@ -47127,19 +47122,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="7" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="B223" s="8">
         <v>45089750000110</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D223" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D223" s="15">
+        <v>999</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="F223" s="7" t="s">
         <v>786</v>
@@ -47147,19 +47142,19 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="7" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B224" s="8">
         <v>46948233000111</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D224" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D224" s="15">
+        <v>999</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="F224" s="7" t="s">
         <v>274</v>
@@ -47167,16 +47162,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="7" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B225" s="8">
         <v>31506529000105</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D225" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D225" s="15">
+        <v>999</v>
       </c>
       <c r="E225" s="7" t="s">
         <v>264</v>
@@ -47187,16 +47182,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="7" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B226" s="8">
         <v>35956874000100</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D226" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D226" s="15">
+        <v>999</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>264</v>
@@ -47207,39 +47202,39 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="7" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B227" s="8">
         <v>44157016000188</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D227" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D227" s="15">
+        <v>999</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>934</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B228" s="8">
         <v>41035989000156</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D228" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D228" s="15">
+        <v>999</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="F228" s="7" t="s">
         <v>440</v>
@@ -47247,16 +47242,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B229" s="8">
         <v>43121014000176</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D229" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D229" s="15">
+        <v>999</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>142</v>
@@ -47267,16 +47262,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="B230" s="8">
         <v>43423186000102</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D230" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D230" s="15">
+        <v>999</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>142</v>
@@ -47287,16 +47282,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B231" s="8">
         <v>48940997000196</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D231" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D231" s="15">
+        <v>999</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>190</v>
@@ -47307,16 +47302,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="B232" s="8">
         <v>52955482000137</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D232" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D232" s="15">
+        <v>999</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>190</v>
@@ -47327,59 +47322,59 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="B233" s="8">
         <v>37567399000105</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D233" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D233" s="15">
+        <v>999</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>1394</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="B234" s="8">
         <v>33378232000137</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D234" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D234" s="15">
+        <v>999</v>
       </c>
       <c r="E234" s="7" t="s">
         <v>1011</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="B235" s="8">
         <v>32770355000156</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D235" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D235" s="15">
+        <v>999</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>786</v>
@@ -47387,19 +47382,19 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="B236" s="8">
         <v>35386842000108</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D236" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D236" s="15">
+        <v>999</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F236" s="7" t="s">
         <v>270</v>
@@ -47407,36 +47402,36 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="B237" s="8">
         <v>35957156000140</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D237" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D237" s="15">
+        <v>999</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="B238" s="8">
         <v>41866372000182</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D238" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D238" s="15">
+        <v>999</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>1609</v>
@@ -47447,39 +47442,39 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="B239" s="8">
         <v>44843813000119</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D239" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D239" s="15">
+        <v>999</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="B240" s="8">
         <v>32239012000160</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D240" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D240" s="15">
+        <v>999</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="F240" s="7" t="s">
         <v>786</v>
@@ -47487,19 +47482,19 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="B241" s="8">
         <v>41802098000188</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D241" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D241" s="15">
+        <v>999</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F241" s="7" t="s">
         <v>274</v>
@@ -47507,19 +47502,19 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="7" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="B242" s="8">
         <v>31569954000143</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D242" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D242" s="15">
+        <v>999</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F242" s="7" t="s">
         <v>274</v>
@@ -47527,39 +47522,39 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="7" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="B243" s="8">
         <v>40526764000130</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D243" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D243" s="15">
+        <v>999</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="7" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="B244" s="8">
         <v>43636185000138</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D244" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D244" s="15">
+        <v>999</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F244" s="7" t="s">
         <v>485</v>
@@ -47567,16 +47562,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="7" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="B245" s="8">
         <v>45299196000103</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D245" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D245" s="15">
+        <v>999</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>42</v>
@@ -47587,199 +47582,199 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="7" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="B246" s="8">
         <v>44814968000127</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D246" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D246" s="15">
+        <v>999</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="7" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="B247" s="8">
         <v>44409412000155</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D247" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D247" s="15">
+        <v>999</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="7" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="B248" s="8">
         <v>34432014000104</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D248" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D248" s="15">
+        <v>999</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>1345</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="B249" s="8">
         <v>33795343000149</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D249" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D249" s="15">
+        <v>999</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="7" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="B250" s="8">
         <v>33784183000132</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D250" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D250" s="15">
+        <v>999</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F250" s="7" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="7" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="B251" s="8">
         <v>32065041000152</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D251" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D251" s="15">
+        <v>999</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F251" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="7" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="B252" s="8">
         <v>24714864000133</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D252" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D252" s="15">
+        <v>999</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F252" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="7" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="B253" s="8">
         <v>27077318000127</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D253" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D253" s="15">
+        <v>999</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F253" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="7" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="B254" s="8">
         <v>47033019000106</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D254" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D254" s="15">
+        <v>999</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="7" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B255" s="8">
         <v>35420532000162</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D255" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D255" s="15">
+        <v>999</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F255" s="7" t="s">
         <v>16</v>
@@ -47787,76 +47782,76 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="7" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="B256" s="8">
         <v>33784231000192</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D256" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D256" s="15">
+        <v>999</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F256" s="7" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="7" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="B257" s="8">
         <v>33755733000195</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D257" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D257" s="15">
+        <v>999</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F257" s="7" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="7" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="B258" s="8">
         <v>37893248000139</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D258" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D258" s="15">
+        <v>999</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>1144</v>
       </c>
       <c r="F258" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="7" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B259" s="8">
         <v>47032970000132</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D259" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D259" s="15">
+        <v>999</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>159</v>
@@ -47867,16 +47862,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="7" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B260" s="8">
         <v>40781137000145</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D260" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D260" s="15">
+        <v>999</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>154</v>
@@ -47887,59 +47882,59 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="7" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B261" s="8">
         <v>36352636000140</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D261" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D261" s="15">
+        <v>999</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="F261" s="7" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="7" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B262" s="8">
         <v>30830240000184</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D262" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D262" s="15">
+        <v>999</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F262" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="7" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="B263" s="8">
         <v>41802040000134</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D263" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D263" s="15">
+        <v>999</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F263" s="7" t="s">
         <v>270</v>
@@ -47947,19 +47942,19 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="7" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B264" s="8">
         <v>30994931000113</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D264" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D264" s="15">
+        <v>999</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F264" s="7" t="s">
         <v>287</v>
@@ -47967,19 +47962,19 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="7" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B265" s="8">
         <v>44230868000153</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D265" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D265" s="15">
+        <v>999</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="F265" s="7" t="s">
         <v>786</v>
@@ -47987,19 +47982,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="B266" s="8">
         <v>32319702000129</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D266" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D266" s="15">
+        <v>999</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="F266" s="7" t="s">
         <v>274</v>
@@ -48007,56 +48002,56 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="7" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B267" s="8">
         <v>33796273000143</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D267" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D267" s="15">
+        <v>999</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="F267" s="7" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B268" s="8">
         <v>31846641000195</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D268" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D268" s="15">
+        <v>999</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>343</v>
       </c>
       <c r="F268" s="7" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="7" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="B269" s="8">
         <v>42718410000112</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D269" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D269" s="15">
+        <v>999</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>343</v>
@@ -48067,16 +48062,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="7" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="B270" s="8">
         <v>31846723000130</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D270" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D270" s="15">
+        <v>999</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>343</v>
@@ -48087,16 +48082,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="7" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="B271" s="8">
         <v>39970216000115</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D271" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D271" s="15">
+        <v>999</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>343</v>
@@ -48107,36 +48102,36 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="7" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B272" s="8">
         <v>41866348000143</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D272" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D272" s="15">
+        <v>999</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>343</v>
       </c>
       <c r="F272" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="7" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B273" s="8">
         <v>44748957000196</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D273" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D273" s="15">
+        <v>999</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>1231</v>
@@ -48147,16 +48142,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="7" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B274" s="8">
         <v>34507447000173</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D274" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D274" s="15">
+        <v>999</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>216</v>
@@ -48167,16 +48162,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="7" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="B275" s="8">
         <v>45645386000127</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D275" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D275" s="15">
+        <v>999</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>216</v>
@@ -48187,56 +48182,56 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="7" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="B276" s="8">
         <v>32346713000106</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D276" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D276" s="15">
+        <v>999</v>
       </c>
       <c r="E276" s="7" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F276" s="7" t="s">
         <v>2099</v>
-      </c>
-      <c r="F276" s="7" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="7" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="B277" s="8">
         <v>43860077000144</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D277" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D277" s="15">
+        <v>999</v>
       </c>
       <c r="E277" s="7" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="F277" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="7" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="B278" s="8">
         <v>34475149000149</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D278" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D278" s="15">
+        <v>999</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>216</v>
@@ -48247,16 +48242,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="7" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="B279" s="8">
         <v>34475199000126</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D279" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D279" s="15">
+        <v>999</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>216</v>
@@ -48267,16 +48262,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="7" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="B280" s="8">
         <v>34475378000163</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D280" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D280" s="15">
+        <v>999</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>216</v>
@@ -48287,16 +48282,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="7" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="B281" s="8">
         <v>34475172000133</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D281" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D281" s="15">
+        <v>999</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>216</v>
@@ -48307,19 +48302,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="7" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="B282" s="8">
         <v>30910166000106</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D282" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D282" s="15">
+        <v>999</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F282" s="7" t="s">
         <v>786</v>
@@ -48327,19 +48322,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="7" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="B283" s="8">
         <v>43636010000120</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D283" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D283" s="15">
+        <v>999</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F283" s="7" t="s">
         <v>786</v>
@@ -48347,19 +48342,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="7" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B284" s="8">
         <v>41035946000170</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D284" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D284" s="15">
+        <v>999</v>
       </c>
       <c r="E284" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F284" s="7" t="s">
         <v>16</v>
@@ -48367,19 +48362,19 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="7" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="B285" s="8">
         <v>36352610000100</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D285" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D285" s="15">
+        <v>999</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F285" s="7" t="s">
         <v>485</v>
@@ -48387,59 +48382,59 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="7" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="B286" s="8">
         <v>32990465000123</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D286" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D286" s="15">
+        <v>999</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F286" s="7" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="7" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="B287" s="8">
         <v>32064950000176</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D287" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D287" s="15">
+        <v>999</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="7" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="B288" s="8">
         <v>52986302000184</v>
       </c>
       <c r="C288" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D288" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D288" s="15">
+        <v>999</v>
       </c>
       <c r="E288" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F288" s="7" t="s">
         <v>786</v>
@@ -48447,99 +48442,99 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="7" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="B289" s="8">
         <v>35744196000103</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D289" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D289" s="15">
+        <v>999</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F289" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="7" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="B290" s="8">
         <v>37900124000133</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D290" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D290" s="15">
+        <v>999</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F290" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="7" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="B291" s="8">
         <v>34430623000116</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D291" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D291" s="15">
+        <v>999</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F291" s="7" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="7" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="B292" s="8">
         <v>34461635000108</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D292" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D292" s="15">
+        <v>999</v>
       </c>
       <c r="E292" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F292" s="7" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="7" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="B293" s="8">
         <v>46099658000101</v>
       </c>
       <c r="C293" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D293" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D293" s="15">
+        <v>999</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F293" s="7" t="s">
         <v>287</v>
@@ -48547,19 +48542,19 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="7" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="B294" s="8">
         <v>34309549000184</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D294" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D294" s="15">
+        <v>999</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F294" s="7" t="s">
         <v>274</v>
@@ -48567,19 +48562,19 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="7" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="B295" s="8">
         <v>37900216000113</v>
       </c>
       <c r="C295" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D295" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D295" s="15">
+        <v>999</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="F295" s="7" t="s">
         <v>270</v>
@@ -48587,19 +48582,19 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="7" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B296" s="8">
         <v>35420569000190</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D296" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D296" s="15">
+        <v>999</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="F296" s="7" t="s">
         <v>270</v>
@@ -48607,19 +48602,19 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="7" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="B297" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D297" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D297" s="15">
+        <v>999</v>
       </c>
       <c r="E297" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F297" s="7" t="s">
         <v>786</v>
@@ -48627,19 +48622,19 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="7" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="B298" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D298" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D298" s="15">
+        <v>999</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F298" s="7" t="s">
         <v>440</v>
@@ -48647,19 +48642,19 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="7" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B299" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D299" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D299" s="15">
+        <v>999</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F299" s="7" t="s">
         <v>16</v>
@@ -48667,19 +48662,19 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="7" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B300" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D300" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D300" s="15">
+        <v>999</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F300" s="7" t="s">
         <v>98</v>
@@ -48687,19 +48682,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="7" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B301" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D301" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D301" s="15">
+        <v>999</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F301" s="7" t="s">
         <v>98</v>
@@ -48707,19 +48702,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="7" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B302" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D302" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D302" s="15">
+        <v>999</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F302" s="7" t="s">
         <v>98</v>
@@ -48727,19 +48722,19 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="7" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="B303" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D303" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D303" s="15">
+        <v>999</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F303" s="7" t="s">
         <v>98</v>
@@ -48747,19 +48742,19 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="7" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B304" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D304" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D304" s="15">
+        <v>999</v>
       </c>
       <c r="E304" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F304" s="7" t="s">
         <v>16</v>
@@ -48767,19 +48762,19 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="7" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B305" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D305" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D305" s="15">
+        <v>999</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F305" s="7" t="s">
         <v>16</v>
@@ -48787,19 +48782,19 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="7" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="B306" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D306" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D306" s="15">
+        <v>999</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F306" s="7" t="s">
         <v>16</v>
@@ -48807,19 +48802,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="7" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="B307" s="8">
         <v>47032813000127</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D307" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D307" s="15">
+        <v>999</v>
       </c>
       <c r="E307" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F307" s="7" t="s">
         <v>16</v>
@@ -48827,19 +48822,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="7" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="B308" s="8">
         <v>47032813000128</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D308" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D308" s="15">
+        <v>999</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F308" s="7" t="s">
         <v>16</v>
@@ -48847,19 +48842,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="7" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B309" s="8">
         <v>47032813000129</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D309" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D309" s="15">
+        <v>999</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F309" s="7" t="s">
         <v>340</v>
@@ -48867,19 +48862,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="7" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B310" s="8">
         <v>39723078000170</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D310" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D310" s="15">
+        <v>999</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F310" s="7" t="s">
         <v>441</v>
@@ -48887,19 +48882,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="7" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B311" s="8">
         <v>63573988000106</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D311" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D311" s="15">
+        <v>999</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F311" s="7" t="s">
         <v>17</v>
@@ -48907,19 +48902,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="7" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B312" s="8">
         <v>63573988000106</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D312" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D312" s="15">
+        <v>999</v>
       </c>
       <c r="E312" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F312" s="7" t="s">
         <v>17</v>
@@ -48927,19 +48922,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="7" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B313" s="8">
         <v>61904092000129</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D313" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D313" s="15">
+        <v>999</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F313" s="7" t="s">
         <v>786</v>
@@ -48947,19 +48942,19 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="7" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="B314" s="8">
         <v>30994931000113</v>
       </c>
       <c r="C314" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D314" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D314" s="15">
+        <v>999</v>
       </c>
       <c r="E314" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F314" s="7" t="s">
         <v>287</v>
@@ -48967,19 +48962,19 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="7" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B315" s="8">
         <v>36620088000191</v>
       </c>
       <c r="C315" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D315" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D315" s="15">
+        <v>999</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F315" s="7" t="s">
         <v>274</v>
@@ -48987,19 +48982,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="7" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B316" s="8">
         <v>58841072000141</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D316" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D316" s="15">
+        <v>999</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F316" s="7" t="s">
         <v>287</v>
@@ -49007,19 +49002,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="7" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="B317" s="8">
         <v>39723078000170</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D317" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D317" s="15">
+        <v>999</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F317" s="7" t="s">
         <v>441</v>
@@ -49027,19 +49022,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="7" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="B318" s="8">
         <v>58841072000141</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D318" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D318" s="15">
+        <v>999</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F318" s="7" t="s">
         <v>287</v>
@@ -49047,19 +49042,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="7" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="B319" s="8">
         <v>30994931000113</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D319" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D319" s="15">
+        <v>999</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F319" s="7" t="s">
         <v>287</v>
@@ -49067,19 +49062,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="7" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B320" s="8">
         <v>63573988000106</v>
       </c>
       <c r="C320" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D320" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D320" s="15">
+        <v>999</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F320" s="7" t="s">
         <v>17</v>
@@ -49087,19 +49082,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="7" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="B321" s="8">
         <v>61904092000129</v>
       </c>
       <c r="C321" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D321" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D321" s="15">
+        <v>999</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F321" s="7" t="s">
         <v>786</v>
@@ -49107,19 +49102,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="7" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B322" s="8">
         <v>63573988000106</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D322" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D322" s="15">
+        <v>999</v>
       </c>
       <c r="E322" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F322" s="7" t="s">
         <v>17</v>
@@ -49127,19 +49122,19 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="7" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="B323" s="8">
         <v>63573988000106</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D323" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D323" s="15">
+        <v>999</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F323" s="7" t="s">
         <v>17</v>
@@ -49147,19 +49142,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="7" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B324" s="8">
         <v>45756511000176</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D324" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D324" s="15">
+        <v>999</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F324" s="7" t="s">
         <v>274</v>
@@ -49167,19 +49162,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="7" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="B325" s="8">
         <v>29562424000121</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D325" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D325" s="15">
+        <v>999</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F325" s="7" t="s">
         <v>17</v>
@@ -49187,19 +49182,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="7" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B326" s="8">
         <v>58841072000141</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D326" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D326" s="15">
+        <v>999</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F326" s="7" t="s">
         <v>287</v>
@@ -49207,19 +49202,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="7" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="B327" s="8">
         <v>36352287000166</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D327" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D327" s="15">
+        <v>999</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F327" s="7" t="s">
         <v>441</v>
@@ -49227,19 +49222,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="7" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B328" s="8">
         <v>58841072000141</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D328" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D328" s="15">
+        <v>999</v>
       </c>
       <c r="E328" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F328" s="7" t="s">
         <v>287</v>
@@ -49247,19 +49242,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="7" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="B329" s="8">
         <v>41866372000182</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D329" s="7" t="s">
-        <v>2385</v>
+        <v>1993</v>
+      </c>
+      <c r="D329" s="15">
+        <v>999</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F329" s="7" t="s">
         <v>485</v>
@@ -49267,19 +49262,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="7" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="B330" s="8">
         <v>40779216000111</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D330" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D330" s="15">
+        <v>999</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F330" s="7" t="s">
         <v>441</v>
@@ -49287,19 +49282,19 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="7" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B331" s="8">
         <v>37893248000139</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D331" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D331" s="15">
+        <v>999</v>
       </c>
       <c r="E331" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F331" s="7" t="s">
         <v>441</v>
@@ -49307,19 +49302,19 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="7" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B332" s="8">
         <v>37893248000139</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D332" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D332" s="15">
+        <v>999</v>
       </c>
       <c r="E332" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F332" s="7" t="s">
         <v>441</v>
@@ -49327,19 +49322,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="7" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="B333" s="8">
         <v>37893248000139</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D333" s="7" t="s">
-        <v>2385</v>
+        <v>1970</v>
+      </c>
+      <c r="D333" s="15">
+        <v>999</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F333" s="7" t="s">
         <v>441</v>
@@ -49347,7 +49342,7 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="7" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="B334" s="8">
         <v>0</v>
@@ -49355,11 +49350,11 @@
       <c r="C334" s="7">
         <v>0</v>
       </c>
-      <c r="D334" s="7" t="s">
-        <v>2385</v>
+      <c r="D334" s="15">
+        <v>999</v>
       </c>
       <c r="E334" s="7" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F334" s="7">
         <v>0</v>

--- a/posicoes/Nome fundos e prev.xlsx
+++ b/posicoes/Nome fundos e prev.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos\Aplicativo Alocação\posicoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DA4F89-4AAA-4D3E-ADBB-546C8752481D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A87B2A-5CB2-4768-879B-EFB08E8274C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28845" yWindow="-16380" windowWidth="29040" windowHeight="15840" xr2:uid="{4AAAD741-8AD6-4B77-B1DE-59D8D73093AB}"/>
+    <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{4AAAD741-8AD6-4B77-B1DE-59D8D73093AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Fundos de Investimentos" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8624" uniqueCount="2439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8632" uniqueCount="2440">
   <si>
     <t>NOME_FUNDO</t>
   </si>
@@ -7347,6 +7347,9 @@
   </si>
   <si>
     <t xml:space="preserve">Liquidação </t>
+  </si>
+  <si>
+    <t>BV CREDITO ATIVO RF CrPr LP FI</t>
   </si>
 </sst>
 </file>
@@ -7556,6 +7559,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{917BF526-EA3A-428E-B1FD-2F26273D6094}" name="Fundos" displayName="Fundos" ref="A1:M978" totalsRowShown="0">
+  <autoFilter ref="A1:M978" xr:uid="{917BF526-EA3A-428E-B1FD-2F26273D6094}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M978">
     <sortCondition ref="A1:A978"/>
   </sortState>
@@ -7875,7 +7879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5965A7DE-001A-43C0-BACC-8E49521C644F}">
-  <dimension ref="A1:M978"/>
+  <dimension ref="A1:M979"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="60.88671875" customWidth="1"/>
@@ -42652,6 +42656,47 @@
         <v>6</v>
       </c>
       <c r="M978" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="979" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A979" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B979" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C979" t="s">
+        <v>231</v>
+      </c>
+      <c r="D979" t="s">
+        <v>16</v>
+      </c>
+      <c r="E979" t="s">
+        <v>786</v>
+      </c>
+      <c r="F979" t="s">
+        <v>18</v>
+      </c>
+      <c r="G979">
+        <v>0</v>
+      </c>
+      <c r="H979">
+        <v>1000</v>
+      </c>
+      <c r="I979">
+        <v>3000</v>
+      </c>
+      <c r="J979">
+        <v>15</v>
+      </c>
+      <c r="K979" t="s">
+        <v>39</v>
+      </c>
+      <c r="L979">
+        <v>1</v>
+      </c>
+      <c r="M979" t="s">
         <v>19</v>
       </c>
     </row>
